--- a/resources/templates/standard/M1200-08.xlsx
+++ b/resources/templates/standard/M1200-08.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="65">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>용접 포인트별 용접장 기준 팁 교환 주기 평가서 (갑지)</t>
   </si>
@@ -1127,13 +1130,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -1180,15 +1185,15 @@
       <c r="AW1" s="2"/>
       <c r="AX1" s="2"/>
       <c r="AY1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA1" s="4"/>
       <c r="BB1" s="4"/>
       <c r="BC1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD1" s="4"/>
       <c r="BE1" s="4"/>
@@ -1313,14 +1318,14 @@
     </row>
     <row r="4" ht="21.95" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -1328,13 +1333,13 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -1355,13 +1360,13 @@
       <c r="AG4" s="9"/>
       <c r="AH4" s="9"/>
       <c r="AI4" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ4" s="8"/>
       <c r="AK4" s="8"/>
       <c r="AL4" s="8"/>
       <c r="AM4" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN4" s="9"/>
       <c r="AO4" s="9"/>
@@ -1384,13 +1389,13 @@
     </row>
     <row r="5" ht="21.95" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -1398,7 +1403,7 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1425,7 +1430,7 @@
       <c r="AH5" s="4"/>
       <c r="AI5" s="4"/>
       <c r="AJ5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
@@ -1461,35 +1466,35 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
       <c r="P6" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
       <c r="U6" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
       <c r="Z6" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
       <c r="AE6" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF6" s="12"/>
       <c r="AG6" s="12"/>
@@ -1520,13 +1525,13 @@
     </row>
     <row r="7" ht="21.95" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
@@ -1534,35 +1539,35 @@
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
       <c r="K7" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
       <c r="O7" s="15"/>
       <c r="P7" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q7" s="15"/>
       <c r="R7" s="15"/>
       <c r="S7" s="15"/>
       <c r="T7" s="15"/>
       <c r="U7" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V7" s="15"/>
       <c r="W7" s="15"/>
       <c r="X7" s="15"/>
       <c r="Y7" s="15"/>
       <c r="Z7" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA7" s="15"/>
       <c r="AB7" s="15"/>
       <c r="AC7" s="15"/>
       <c r="AD7" s="15"/>
       <c r="AE7" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF7" s="16"/>
       <c r="AG7" s="16"/>
@@ -1597,7 +1602,7 @@
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
@@ -1605,7 +1610,7 @@
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
@@ -1672,7 +1677,7 @@
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
@@ -1680,7 +1685,7 @@
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
@@ -1747,7 +1752,7 @@
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="21"/>
       <c r="G10" s="21"/>
@@ -1755,7 +1760,7 @@
       <c r="I10" s="21"/>
       <c r="J10" s="21"/>
       <c r="K10" s="22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L10" s="22"/>
       <c r="M10" s="22"/>
@@ -1822,7 +1827,7 @@
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
@@ -1830,7 +1835,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
       <c r="K11" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
@@ -1897,7 +1902,7 @@
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="28"/>
       <c r="G12" s="28"/>
@@ -2072,13 +2077,13 @@
     </row>
     <row r="15" ht="21.95" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2086,7 +2091,7 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -2128,7 +2133,7 @@
       <c r="AW15" s="4"/>
       <c r="AX15" s="4"/>
       <c r="AY15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ15" s="4"/>
       <c r="BA15" s="4"/>
@@ -2149,56 +2154,56 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
       <c r="P16" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
       <c r="U16" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
       <c r="Z16" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
       <c r="AC16" s="11"/>
       <c r="AD16" s="11"/>
       <c r="AE16" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF16" s="11"/>
       <c r="AG16" s="11"/>
       <c r="AH16" s="11"/>
       <c r="AI16" s="11"/>
       <c r="AJ16" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AK16" s="11"/>
       <c r="AL16" s="11"/>
       <c r="AM16" s="11"/>
       <c r="AN16" s="11"/>
       <c r="AO16" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AP16" s="11"/>
       <c r="AQ16" s="11"/>
       <c r="AR16" s="11"/>
       <c r="AS16" s="11"/>
       <c r="AT16" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU16" s="12"/>
       <c r="AV16" s="12"/>
@@ -2214,13 +2219,13 @@
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -2228,56 +2233,56 @@
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
       <c r="K17" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
       <c r="P17" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q17" s="15"/>
       <c r="R17" s="15"/>
       <c r="S17" s="15"/>
       <c r="T17" s="15"/>
       <c r="U17" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V17" s="15"/>
       <c r="W17" s="15"/>
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
       <c r="Z17" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA17" s="15"/>
       <c r="AB17" s="15"/>
       <c r="AC17" s="15"/>
       <c r="AD17" s="15"/>
       <c r="AE17" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF17" s="15"/>
       <c r="AG17" s="15"/>
       <c r="AH17" s="15"/>
       <c r="AI17" s="15"/>
       <c r="AJ17" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK17" s="15"/>
       <c r="AL17" s="15"/>
       <c r="AM17" s="15"/>
       <c r="AN17" s="15"/>
       <c r="AO17" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AP17" s="15"/>
       <c r="AQ17" s="15"/>
       <c r="AR17" s="15"/>
       <c r="AS17" s="15"/>
       <c r="AT17" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AU17" s="16"/>
       <c r="AV17" s="16"/>
@@ -2297,7 +2302,7 @@
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="30"/>
       <c r="G18" s="30"/>
@@ -2305,7 +2310,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
       <c r="K18" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L18" s="31"/>
       <c r="M18" s="31"/>
@@ -2381,7 +2386,7 @@
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
@@ -2389,7 +2394,7 @@
       <c r="I19" s="24"/>
       <c r="J19" s="24"/>
       <c r="K19" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
@@ -2465,7 +2470,7 @@
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F20" s="28"/>
       <c r="G20" s="28"/>
@@ -2640,13 +2645,13 @@
     </row>
     <row r="23" ht="21.95" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2654,7 +2659,7 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L23" s="33"/>
       <c r="M23" s="33"/>
@@ -2686,7 +2691,7 @@
       <c r="AM23" s="33"/>
       <c r="AN23" s="33"/>
       <c r="AO23" s="34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP23" s="34"/>
       <c r="AQ23" s="34"/>
@@ -2717,42 +2722,42 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11"/>
       <c r="P24" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
       <c r="T24" s="11"/>
       <c r="U24" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
       <c r="Z24" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA24" s="11"/>
       <c r="AB24" s="11"/>
       <c r="AC24" s="11"/>
       <c r="AD24" s="11"/>
       <c r="AE24" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF24" s="11"/>
       <c r="AG24" s="11"/>
       <c r="AH24" s="11"/>
       <c r="AI24" s="11"/>
       <c r="AJ24" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK24" s="12"/>
       <c r="AL24" s="12"/>
@@ -2778,13 +2783,13 @@
     </row>
     <row r="25" ht="21.95" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
@@ -2792,42 +2797,42 @@
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
       <c r="K25" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q25" s="15"/>
       <c r="R25" s="15"/>
       <c r="S25" s="15"/>
       <c r="T25" s="15"/>
       <c r="U25" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V25" s="15"/>
       <c r="W25" s="15"/>
       <c r="X25" s="15"/>
       <c r="Y25" s="15"/>
       <c r="Z25" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA25" s="15"/>
       <c r="AB25" s="15"/>
       <c r="AC25" s="15"/>
       <c r="AD25" s="15"/>
       <c r="AE25" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF25" s="15"/>
       <c r="AG25" s="15"/>
       <c r="AH25" s="15"/>
       <c r="AI25" s="15"/>
       <c r="AJ25" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK25" s="16"/>
       <c r="AL25" s="16"/>
@@ -2857,7 +2862,7 @@
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
@@ -2865,7 +2870,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
       <c r="K26" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
@@ -2935,7 +2940,7 @@
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
       <c r="E27" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
@@ -2943,7 +2948,7 @@
       <c r="I27" s="24"/>
       <c r="J27" s="24"/>
       <c r="K27" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L27" s="25"/>
       <c r="M27" s="25"/>
@@ -3013,7 +3018,7 @@
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
@@ -3192,7 +3197,7 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F31" s="36"/>
       <c r="G31" s="36"/>
@@ -3427,7 +3432,7 @@
     <row r="35" ht="23.1" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A35" s="40"/>
       <c r="B35" s="41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C35" s="41"/>
       <c r="D35" s="41"/>
@@ -3464,7 +3469,7 @@
       <c r="AI35" s="41"/>
       <c r="AJ35" s="42"/>
       <c r="AK35" s="43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AL35" s="43"/>
       <c r="AM35" s="43"/>
@@ -4352,14 +4357,14 @@
       <c r="AJ50" s="42"/>
       <c r="AK50" s="51"/>
       <c r="AL50" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AM50" s="29"/>
       <c r="AN50" s="29"/>
       <c r="AO50" s="29"/>
       <c r="AP50" s="29"/>
       <c r="AQ50" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AR50" s="25"/>
       <c r="AS50" s="25"/>
@@ -4370,7 +4375,7 @@
       <c r="AX50" s="25"/>
       <c r="AY50" s="25"/>
       <c r="AZ50" s="52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BA50" s="52"/>
       <c r="BB50" s="52"/>
@@ -4476,14 +4481,14 @@
       <c r="AJ52" s="42"/>
       <c r="AK52" s="51"/>
       <c r="AL52" s="54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM52" s="54"/>
       <c r="AN52" s="54"/>
       <c r="AO52" s="54"/>
       <c r="AP52" s="54"/>
       <c r="AQ52" s="55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AR52" s="55"/>
       <c r="AS52" s="55"/>
@@ -4494,7 +4499,7 @@
       <c r="AX52" s="55"/>
       <c r="AY52" s="55"/>
       <c r="AZ52" s="52" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BA52" s="52"/>
       <c r="BB52" s="52"/>
@@ -4600,14 +4605,14 @@
       <c r="AJ54" s="42"/>
       <c r="AK54" s="51"/>
       <c r="AL54" s="54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AM54" s="54"/>
       <c r="AN54" s="54"/>
       <c r="AO54" s="54"/>
       <c r="AP54" s="54"/>
       <c r="AQ54" s="55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AR54" s="55"/>
       <c r="AS54" s="55"/>
@@ -4618,7 +4623,7 @@
       <c r="AX54" s="55"/>
       <c r="AY54" s="55"/>
       <c r="AZ54" s="56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BA54" s="56"/>
       <c r="BB54" s="56"/>
@@ -4724,14 +4729,14 @@
       <c r="AJ56" s="42"/>
       <c r="AK56" s="51"/>
       <c r="AL56" s="54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM56" s="54"/>
       <c r="AN56" s="54"/>
       <c r="AO56" s="54"/>
       <c r="AP56" s="54"/>
       <c r="AQ56" s="55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AR56" s="55"/>
       <c r="AS56" s="55"/>
